--- a/17 18 20/Excel/6.Project/Inventory Managment/Paris Summary.xlsx
+++ b/17 18 20/Excel/6.Project/Inventory Managment/Paris Summary.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="4" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="81">
   <si>
     <t>Cut_off</t>
   </si>
@@ -256,25 +256,29 @@
     <t>Column2</t>
   </si>
   <si>
-    <t>Cut off</t>
-  </si>
-  <si>
     <t>Sr No2</t>
   </si>
   <si>
     <t>Cutof</t>
+  </si>
+  <si>
+    <t>CNFD</t>
+  </si>
+  <si>
+    <t>LOUVRE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="dd/mm/yy"/>
     <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="[$-14009]dd/mm/yy;@"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -298,6 +302,26 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Courier New"/>
       <family val="3"/>
@@ -330,24 +354,54 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="2" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="15" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Accent2" xfId="2" builtinId="33"/>
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+  <dxfs count="40">
+    <dxf>
+      <numFmt numFmtId="167" formatCode="[$-14009]dd/mm/yy;@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="Courier New"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -356,21 +410,8 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Courier New"/>
-        <scheme val="none"/>
+        <sz val="9"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="dd/mm/yy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="20" formatCode="dd/mmm/yy"/>
     </dxf>
     <dxf>
       <font>
@@ -379,24 +420,8 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Courier New"/>
-        <scheme val="none"/>
+        <sz val="9"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="20" formatCode="dd/mmm/yy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="20" formatCode="dd/mmm/yy"/>
     </dxf>
     <dxf>
       <font>
@@ -405,24 +430,206 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+      </font>
+      <numFmt numFmtId="20" formatCode="dd/mmm/yy"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+      </font>
+      <numFmt numFmtId="20" formatCode="dd/mmm/yy"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
         <color theme="1"/>
         <name val="Courier New"/>
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="dd/mm/yy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="dd/mm/yy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="dd/mm/yy"/>
     </dxf>
     <dxf>
       <font>
@@ -440,6 +647,112 @@
         <name val="Courier New"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Courier New"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Courier New"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="dd/mm/yy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="dd/mm/yy"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Courier New"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="dd/mm/yy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="dd/mm/yy"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Courier New"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="20" formatCode="dd/mmm/yy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Courier New"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -455,19 +768,31 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Sum" displayName="Sum" ref="A4:G17" totalsRowShown="0">
-  <autoFilter ref="A4:G17"/>
-  <tableColumns count="7">
-    <tableColumn id="1" name="Code" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Sum" displayName="Sum" ref="A4:K17" totalsRowShown="0">
+  <autoFilter ref="A4:K17"/>
+  <tableColumns count="11">
+    <tableColumn id="1" name="Code" dataDxfId="39">
       <calculatedColumnFormula>VLOOKUP(Sum[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Sum[[#This Row],[Tour Date]],"ddmm")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" name="Column1" dataDxfId="2"/>
+    <tableColumn id="8" name="Column2" dataDxfId="27">
+      <calculatedColumnFormula>VLOOKUP(Sum[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Sum[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;"CNFD"</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" name="Column1" dataDxfId="38"/>
     <tableColumn id="5" name="Sr No2"/>
-    <tableColumn id="2" name="Tour Date" dataDxfId="4"/>
+    <tableColumn id="2" name="Tour Date" dataDxfId="37"/>
     <tableColumn id="3" name="Tour Name"/>
     <tableColumn id="4" name="Dept"/>
-    <tableColumn id="7" name="Cutof" dataDxfId="0" dataCellStyle="Comma">
-      <calculatedColumnFormula>COUNTIFS(MSF[[#All],[Cut_off]],Summary!$G$2,MSF[[#All],[Code]],Sum[[#This Row],[Code]])</calculatedColumnFormula>
+    <tableColumn id="11" name="MSF" dataDxfId="0">
+      <calculatedColumnFormula>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],MSF[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" name="LOUVRE" dataDxfId="2">
+      <calculatedColumnFormula>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],Louvre[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" name="Accor" dataDxfId="1">
+      <calculatedColumnFormula>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],Accor[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="7" name="Cutof" dataDxfId="36" dataCellStyle="Comma">
+      <calculatedColumnFormula>COUNTIFS(MSF[[#All],[Cut_off]],Summary!$K$2,MSF[[#All],[Code]],Sum[[#This Row],[Code]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -475,19 +800,22 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MSF" displayName="MSF" ref="A1:R14" totalsRowShown="0" headerRowCellStyle="Accent2">
-  <autoFilter ref="A1:R14"/>
-  <tableColumns count="18">
-    <tableColumn id="1" name="Code" dataDxfId="15">
-      <calculatedColumnFormula>VLOOKUP(G2,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(F2,"DDMM")</calculatedColumnFormula>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MSF" displayName="MSF" ref="A2:S15" totalsRowShown="0" headerRowCellStyle="Accent2">
+  <autoFilter ref="A2:S15"/>
+  <tableColumns count="19">
+    <tableColumn id="1" name="Code" dataDxfId="35">
+      <calculatedColumnFormula>VLOOKUP(H3,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(G3,"DDMM")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" name="Cut_off" dataDxfId="14">
-      <calculatedColumnFormula>F2-30</calculatedColumnFormula>
+    <tableColumn id="20" name="Column1" dataDxfId="28">
+      <calculatedColumnFormula>VLOOKUP(H3,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(G3,"DDMM")&amp;"."&amp;MSF[[#This Row],[Status-1]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" name="Cut_off" dataDxfId="34">
+      <calculatedColumnFormula>G3-30</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" name="Sr.No."/>
     <tableColumn id="4" name="Region"/>
     <tableColumn id="5" name="City(Area)"/>
-    <tableColumn id="6" name="Tour Date" dataDxfId="13"/>
+    <tableColumn id="6" name="Tour Date" dataDxfId="33"/>
     <tableColumn id="7" name="Tour Name"/>
     <tableColumn id="8" name="Dept"/>
     <tableColumn id="9" name="Status-1"/>
@@ -506,19 +834,22 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Louvre" displayName="Louvre" ref="A1:T14" totalsRowShown="0" headerRowCellStyle="Accent2">
-  <autoFilter ref="A1:T14"/>
-  <tableColumns count="20">
-    <tableColumn id="1" name="Code" dataDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Louvre" displayName="Louvre" ref="A2:U15" totalsRowShown="0" headerRowCellStyle="Accent2">
+  <autoFilter ref="A2:U15"/>
+  <tableColumns count="21">
+    <tableColumn id="1" name="Code" dataDxfId="32">
       <calculatedColumnFormula>VLOOKUP(Louvre[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Louvre[[#This Row],[Tour Date]],"ddmm")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" name="Cut_off" dataDxfId="3">
-      <calculatedColumnFormula>F2-40</calculatedColumnFormula>
+    <tableColumn id="21" name="Column1" dataDxfId="26">
+      <calculatedColumnFormula>VLOOKUP(Louvre[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Louvre[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;Louvre[[#This Row],[Status-1]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" name="Sr.No." dataDxfId="11"/>
+    <tableColumn id="2" name="Cut_off" dataDxfId="31">
+      <calculatedColumnFormula>G3-40</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" name="Sr.No." dataDxfId="30"/>
     <tableColumn id="4" name="Region"/>
     <tableColumn id="5" name="City(Area)"/>
-    <tableColumn id="6" name="Tour Date" dataDxfId="12"/>
+    <tableColumn id="6" name="Tour Date" dataDxfId="29"/>
     <tableColumn id="7" name="Tour Name"/>
     <tableColumn id="8" name="Dept"/>
     <tableColumn id="9" name="Status-1"/>
@@ -539,33 +870,36 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Accor" displayName="Accor" ref="A1:T14" totalsRowShown="0" headerRowCellStyle="Accent2">
-  <autoFilter ref="A1:T14"/>
-  <tableColumns count="20">
-    <tableColumn id="1" name="Code" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Accor" displayName="Accor" ref="A2:U15" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4" headerRowCellStyle="Accent2">
+  <autoFilter ref="A2:U15"/>
+  <tableColumns count="21">
+    <tableColumn id="1" name="Code" dataDxfId="25">
       <calculatedColumnFormula>VLOOKUP(Accor[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Accor[[#This Row],[Tour Date]],"ddmm")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" name="Cut_off" dataDxfId="7">
-      <calculatedColumnFormula>F2-30</calculatedColumnFormula>
+    <tableColumn id="21" name="Column1" dataDxfId="3">
+      <calculatedColumnFormula>VLOOKUP(Accor[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Accor[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;Accor[[#This Row],[Status-1]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" name="Sr.No." dataDxfId="8"/>
-    <tableColumn id="4" name="Region" dataDxfId="6"/>
-    <tableColumn id="5" name="City(Area)"/>
-    <tableColumn id="6" name="Tour Date" dataDxfId="9"/>
-    <tableColumn id="7" name="Tour Name"/>
-    <tableColumn id="8" name="Dept"/>
-    <tableColumn id="9" name="Status-1"/>
-    <tableColumn id="10" name="Supplier"/>
-    <tableColumn id="11" name="Hotel-1"/>
-    <tableColumn id="12" name="Options"/>
-    <tableColumn id="13" name="SGL"/>
-    <tableColumn id="14" name="DBL"/>
-    <tableColumn id="15" name="TPL"/>
-    <tableColumn id="16" name="TOTAL"/>
-    <tableColumn id="17" name="Operating"/>
-    <tableColumn id="18" name="CtOF"/>
-    <tableColumn id="19" name="Operating2"/>
-    <tableColumn id="20" name="CtOF3"/>
+    <tableColumn id="2" name="Cut_off" dataDxfId="24">
+      <calculatedColumnFormula>G3-30</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" name="Sr.No." dataDxfId="23"/>
+    <tableColumn id="4" name="Region" dataDxfId="22"/>
+    <tableColumn id="5" name="City(Area)" dataDxfId="21"/>
+    <tableColumn id="6" name="Tour Date" dataDxfId="20"/>
+    <tableColumn id="7" name="Tour Name" dataDxfId="19"/>
+    <tableColumn id="8" name="Dept" dataDxfId="18"/>
+    <tableColumn id="9" name="Status-1" dataDxfId="17"/>
+    <tableColumn id="10" name="Supplier" dataDxfId="16"/>
+    <tableColumn id="11" name="Hotel-1" dataDxfId="15"/>
+    <tableColumn id="12" name="Options" dataDxfId="14"/>
+    <tableColumn id="13" name="SGL" dataDxfId="13"/>
+    <tableColumn id="14" name="DBL" dataDxfId="12"/>
+    <tableColumn id="15" name="TPL" dataDxfId="11"/>
+    <tableColumn id="16" name="TOTAL" dataDxfId="10"/>
+    <tableColumn id="17" name="Operating" dataDxfId="9"/>
+    <tableColumn id="18" name="CtOF" dataDxfId="8"/>
+    <tableColumn id="19" name="Operating2" dataDxfId="7"/>
+    <tableColumn id="20" name="CtOF3" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -845,346 +1179,567 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="7.21875" customWidth="1"/>
-    <col min="4" max="4" width="11.109375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="39.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.88671875" customWidth="1"/>
+    <col min="2" max="2" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
+    <col min="4" max="4" width="7.21875" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="39.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.88671875" customWidth="1"/>
+    <col min="8" max="10" width="13.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="F1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G2" s="1">
-        <v>46218</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E1"/>
+    </row>
+    <row r="2" spans="1:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E2"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E3"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" t="s">
         <v>75</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" t="s">
+        <v>80</v>
+      </c>
+      <c r="J4" t="s">
+        <v>44</v>
+      </c>
+      <c r="K4" t="s">
         <v>78</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="str">
         <f>VLOOKUP(Sum[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Sum[[#This Row],[Tour Date]],"ddmm")</f>
         <v>GY.MINI.0208</v>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2">
+      <c r="B5" s="5" t="str">
+        <f>VLOOKUP(Sum[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Sum[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;"CNFD"</f>
+        <v>GY.MINI.0208.CNFD</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2">
         <v>46236</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>17</v>
       </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5" s="7">
-        <f>COUNTIFS(MSF[[#All],[Cut_off]],Summary!$G$2,MSF[[#All],[Code]],Sum[[#This Row],[Code]])</f>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="13" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],MSF[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>CNFD</v>
+      </c>
+      <c r="I5" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],Louvre[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>Not Confirmed</v>
+      </c>
+      <c r="J5" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],Accor[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>Not Confirmed</v>
+      </c>
+      <c r="K5" s="6">
+        <f>COUNTIFS(MSF[[#All],[Cut_off]],Summary!$K$2,MSF[[#All],[Code]],Sum[[#This Row],[Code]])</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="str">
         <f>VLOOKUP(Sum[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Sum[[#This Row],[Tour Date]],"ddmm")</f>
         <v>NR.SWGL.0308</v>
       </c>
-      <c r="C6">
-        <f>C5+1</f>
+      <c r="B6" s="5" t="str">
+        <f>VLOOKUP(Sum[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Sum[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;"CNFD"</f>
+        <v>NR.SWGL.0308.CNFD</v>
+      </c>
+      <c r="D6">
+        <f>D5+1</f>
         <v>2</v>
       </c>
-      <c r="D6" s="2">
+      <c r="E6" s="2">
         <v>46237</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>21</v>
       </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6" s="7">
-        <f>COUNTIFS(MSF[[#All],[Cut_off]],Summary!$G$2,MSF[[#All],[Code]],Sum[[#This Row],[Code]])</f>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6" s="13" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],MSF[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>CNFD</v>
+      </c>
+      <c r="I6" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],Louvre[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>Not Confirmed</v>
+      </c>
+      <c r="J6" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],Accor[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>Not Confirmed</v>
+      </c>
+      <c r="K6" s="6">
+        <f>COUNTIFS(MSF[[#All],[Cut_off]],Summary!$K$2,MSF[[#All],[Code]],Sum[[#This Row],[Code]])</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="str">
         <f>VLOOKUP(Sum[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Sum[[#This Row],[Tour Date]],"ddmm")</f>
         <v>NR.EUCH.0408</v>
       </c>
-      <c r="C7">
-        <f t="shared" ref="C7:C17" si="0">C6+1</f>
+      <c r="B7" s="5" t="str">
+        <f>VLOOKUP(Sum[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Sum[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;"CNFD"</f>
+        <v>NR.EUCH.0408.CNFD</v>
+      </c>
+      <c r="D7">
+        <f t="shared" ref="D7:D17" si="0">D6+1</f>
         <v>3</v>
       </c>
-      <c r="D7" s="2">
+      <c r="E7" s="2">
         <v>46238</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>23</v>
       </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7" s="7">
-        <f>COUNTIFS(MSF[[#All],[Cut_off]],Summary!$G$2,MSF[[#All],[Code]],Sum[[#This Row],[Code]])</f>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7" s="13" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],MSF[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>Not Confirmed</v>
+      </c>
+      <c r="I7" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],Louvre[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>CNFD</v>
+      </c>
+      <c r="J7" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],Accor[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>Not Confirmed</v>
+      </c>
+      <c r="K7" s="6">
+        <f>COUNTIFS(MSF[[#All],[Cut_off]],Summary!$K$2,MSF[[#All],[Code]],Sum[[#This Row],[Code]])</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="str">
         <f>VLOOKUP(Sum[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Sum[[#This Row],[Tour Date]],"ddmm")</f>
         <v>GY.MINI.0508</v>
       </c>
-      <c r="C8">
+      <c r="B8" s="5" t="str">
+        <f>VLOOKUP(Sum[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Sum[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;"CNFD"</f>
+        <v>GY.MINI.0508.CNFD</v>
+      </c>
+      <c r="D8">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="D8" s="2">
+      <c r="E8" s="2">
         <v>46239</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>17</v>
       </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8" s="7">
-        <f>COUNTIFS(MSF[[#All],[Cut_off]],Summary!$G$2,MSF[[#All],[Code]],Sum[[#This Row],[Code]])</f>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8" s="13" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],MSF[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>Not Confirmed</v>
+      </c>
+      <c r="I8" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],Louvre[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>CNFD</v>
+      </c>
+      <c r="J8" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],Accor[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>Not Confirmed</v>
+      </c>
+      <c r="K8" s="6">
+        <f>COUNTIFS(MSF[[#All],[Cut_off]],Summary!$K$2,MSF[[#All],[Code]],Sum[[#This Row],[Code]])</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="str">
         <f>VLOOKUP(Sum[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Sum[[#This Row],[Tour Date]],"ddmm")</f>
         <v>NR.EUCH.0608</v>
       </c>
-      <c r="C9">
+      <c r="B9" s="5" t="str">
+        <f>VLOOKUP(Sum[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Sum[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;"CNFD"</f>
+        <v>NR.EUCH.0608.CNFD</v>
+      </c>
+      <c r="D9">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="D9" s="2">
+      <c r="E9" s="2">
         <v>46240</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>23</v>
       </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9" s="7">
-        <f>COUNTIFS(MSF[[#All],[Cut_off]],Summary!$G$2,MSF[[#All],[Code]],Sum[[#This Row],[Code]])</f>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9" s="13" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],MSF[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>Not Confirmed</v>
+      </c>
+      <c r="I9" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],Louvre[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>Not Confirmed</v>
+      </c>
+      <c r="J9" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],Accor[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>Not Confirmed</v>
+      </c>
+      <c r="K9" s="6">
+        <f>COUNTIFS(MSF[[#All],[Cut_off]],Summary!$K$2,MSF[[#All],[Code]],Sum[[#This Row],[Code]])</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="str">
         <f>VLOOKUP(Sum[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Sum[[#This Row],[Tour Date]],"ddmm")</f>
         <v>GY.MGKE.0708</v>
       </c>
-      <c r="C10">
+      <c r="B10" s="5" t="str">
+        <f>VLOOKUP(Sum[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Sum[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;"CNFD"</f>
+        <v>GY.MGKE.0708.CNFD</v>
+      </c>
+      <c r="D10">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="D10" s="2">
+      <c r="E10" s="2">
         <v>46241</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>25</v>
       </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10" s="7">
-        <f>COUNTIFS(MSF[[#All],[Cut_off]],Summary!$G$2,MSF[[#All],[Code]],Sum[[#This Row],[Code]])</f>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" s="13" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],MSF[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>Not Confirmed</v>
+      </c>
+      <c r="I10" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],Louvre[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>Not Confirmed</v>
+      </c>
+      <c r="J10" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],Accor[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>CNFD</v>
+      </c>
+      <c r="K10" s="6">
+        <f>COUNTIFS(MSF[[#All],[Cut_off]],Summary!$K$2,MSF[[#All],[Code]],Sum[[#This Row],[Code]])</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="str">
         <f>VLOOKUP(Sum[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Sum[[#This Row],[Tour Date]],"ddmm")</f>
         <v>NR.TAEU.0808</v>
       </c>
-      <c r="C11">
+      <c r="B11" s="5" t="str">
+        <f>VLOOKUP(Sum[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Sum[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;"CNFD"</f>
+        <v>NR.TAEU.0808.CNFD</v>
+      </c>
+      <c r="D11">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="D11" s="2">
+      <c r="E11" s="2">
         <v>46242</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>26</v>
       </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11" s="7">
-        <f>COUNTIFS(MSF[[#All],[Cut_off]],Summary!$G$2,MSF[[#All],[Code]],Sum[[#This Row],[Code]])</f>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11" s="13" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],MSF[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>Not Confirmed</v>
+      </c>
+      <c r="I11" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],Louvre[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>Not Confirmed</v>
+      </c>
+      <c r="J11" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],Accor[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>CNFD</v>
+      </c>
+      <c r="K11" s="6">
+        <f>COUNTIFS(MSF[[#All],[Cut_off]],Summary!$K$2,MSF[[#All],[Code]],Sum[[#This Row],[Code]])</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="str">
         <f>VLOOKUP(Sum[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Sum[[#This Row],[Tour Date]],"ddmm")</f>
         <v>NR.SWGL.0908</v>
       </c>
-      <c r="C12">
+      <c r="B12" s="5" t="str">
+        <f>VLOOKUP(Sum[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Sum[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;"CNFD"</f>
+        <v>NR.SWGL.0908.CNFD</v>
+      </c>
+      <c r="D12">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="D12" s="2">
+      <c r="E12" s="2">
         <v>46243</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>21</v>
       </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12" s="7">
-        <f>COUNTIFS(MSF[[#All],[Cut_off]],Summary!$G$2,MSF[[#All],[Code]],Sum[[#This Row],[Code]])</f>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12" s="13" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],MSF[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>Not Confirmed</v>
+      </c>
+      <c r="I12" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],Louvre[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>Not Confirmed</v>
+      </c>
+      <c r="J12" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],Accor[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>Not Confirmed</v>
+      </c>
+      <c r="K12" s="6">
+        <f>COUNTIFS(MSF[[#All],[Cut_off]],Summary!$K$2,MSF[[#All],[Code]],Sum[[#This Row],[Code]])</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="str">
         <f>VLOOKUP(Sum[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Sum[[#This Row],[Tour Date]],"ddmm")</f>
         <v>DD.WHRL.1008</v>
       </c>
-      <c r="C13">
+      <c r="B13" s="5" t="str">
+        <f>VLOOKUP(Sum[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Sum[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;"CNFD"</f>
+        <v>DD.WHRL.1008.CNFD</v>
+      </c>
+      <c r="D13">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="D13" s="2">
+      <c r="E13" s="2">
         <v>46244</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>28</v>
       </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13" s="7">
-        <f>COUNTIFS(MSF[[#All],[Cut_off]],Summary!$G$2,MSF[[#All],[Code]],Sum[[#This Row],[Code]])</f>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13" s="13" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],MSF[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>Not Confirmed</v>
+      </c>
+      <c r="I13" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],Louvre[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>Not Confirmed</v>
+      </c>
+      <c r="J13" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],Accor[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>Not Confirmed</v>
+      </c>
+      <c r="K13" s="6">
+        <f>COUNTIFS(MSF[[#All],[Cut_off]],Summary!$K$2,MSF[[#All],[Code]],Sum[[#This Row],[Code]])</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="str">
         <f>VLOOKUP(Sum[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Sum[[#This Row],[Tour Date]],"ddmm")</f>
         <v>GY.MINI.1108</v>
       </c>
-      <c r="C14">
+      <c r="B14" s="5" t="str">
+        <f>VLOOKUP(Sum[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Sum[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;"CNFD"</f>
+        <v>GY.MINI.1108.CNFD</v>
+      </c>
+      <c r="D14">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="D14" s="2">
+      <c r="E14" s="2">
         <v>46245</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>17</v>
       </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14" s="7">
-        <f>COUNTIFS(MSF[[#All],[Cut_off]],Summary!$G$2,MSF[[#All],[Code]],Sum[[#This Row],[Code]])</f>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="13" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],MSF[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>Not Confirmed</v>
+      </c>
+      <c r="I14" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],Louvre[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>Not Confirmed</v>
+      </c>
+      <c r="J14" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],Accor[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>Not Confirmed</v>
+      </c>
+      <c r="K14" s="6">
+        <f>COUNTIFS(MSF[[#All],[Cut_off]],Summary!$K$2,MSF[[#All],[Code]],Sum[[#This Row],[Code]])</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="str">
         <f>VLOOKUP(Sum[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Sum[[#This Row],[Tour Date]],"ddmm")</f>
         <v>NR.EUCH.1208</v>
       </c>
-      <c r="C15">
+      <c r="B15" s="5" t="str">
+        <f>VLOOKUP(Sum[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Sum[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;"CNFD"</f>
+        <v>NR.EUCH.1208.CNFD</v>
+      </c>
+      <c r="D15">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="D15" s="2">
+      <c r="E15" s="2">
         <v>46246</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>23</v>
       </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15" s="7">
-        <f>COUNTIFS(MSF[[#All],[Cut_off]],Summary!$G$2,MSF[[#All],[Code]],Sum[[#This Row],[Code]])</f>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15" s="13" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],MSF[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>Not Confirmed</v>
+      </c>
+      <c r="I15" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],Louvre[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>Not Confirmed</v>
+      </c>
+      <c r="J15" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],Accor[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>Not Confirmed</v>
+      </c>
+      <c r="K15" s="6">
+        <f>COUNTIFS(MSF[[#All],[Cut_off]],Summary!$K$2,MSF[[#All],[Code]],Sum[[#This Row],[Code]])</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="str">
         <f>VLOOKUP(Sum[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Sum[[#This Row],[Tour Date]],"ddmm")</f>
         <v>DD.FSME.1308</v>
       </c>
-      <c r="C16">
+      <c r="B16" s="5" t="str">
+        <f>VLOOKUP(Sum[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Sum[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;"CNFD"</f>
+        <v>DD.FSME.1308.CNFD</v>
+      </c>
+      <c r="D16">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="D16" s="2">
+      <c r="E16" s="2">
         <v>46247</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>30</v>
       </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16" s="7">
-        <f>COUNTIFS(MSF[[#All],[Cut_off]],Summary!$G$2,MSF[[#All],[Code]],Sum[[#This Row],[Code]])</f>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16" s="13" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],MSF[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>Not Confirmed</v>
+      </c>
+      <c r="I16" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],Louvre[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>Not Confirmed</v>
+      </c>
+      <c r="J16" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],Accor[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>Not Confirmed</v>
+      </c>
+      <c r="K16" s="6">
+        <f>COUNTIFS(MSF[[#All],[Cut_off]],Summary!$K$2,MSF[[#All],[Code]],Sum[[#This Row],[Code]])</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="str">
         <f>VLOOKUP(Sum[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Sum[[#This Row],[Tour Date]],"ddmm")</f>
         <v>DD.MRVL.1408</v>
       </c>
-      <c r="C17">
+      <c r="B17" s="5" t="str">
+        <f>VLOOKUP(Sum[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Sum[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;"CNFD"</f>
+        <v>DD.MRVL.1408.CNFD</v>
+      </c>
+      <c r="D17">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="D17" s="2">
+      <c r="E17" s="2">
         <v>46248</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>31</v>
       </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-      <c r="G17" s="7">
-        <f>COUNTIFS(MSF[[#All],[Cut_off]],Summary!$G$2,MSF[[#All],[Code]],Sum[[#This Row],[Code]])</f>
-        <v>1</v>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17" s="13" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],MSF[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>Not Confirmed</v>
+      </c>
+      <c r="I17" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],Louvre[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>Not Confirmed</v>
+      </c>
+      <c r="J17" t="str">
+        <f>IFERROR(VLOOKUP(Sum[[#This Row],[Column2]],Accor[[#All],[Column1]:[Status-1]],9,FALSE),"Not Confirmed")</f>
+        <v>Not Confirmed</v>
+      </c>
+      <c r="K17" s="6">
+        <f>COUNTIFS(MSF[[#All],[Cut_off]],Summary!$K$2,MSF[[#All],[Code]],Sum[[#This Row],[Code]])</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1197,484 +1752,540 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R14"/>
+  <dimension ref="A2:S15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.33203125" style="5" customWidth="1"/>
-    <col min="5" max="6" width="10.6640625" customWidth="1"/>
-    <col min="7" max="7" width="39.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="9.109375" customWidth="1"/>
-    <col min="17" max="17" width="10.6640625" customWidth="1"/>
+    <col min="2" max="2" width="22.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.6640625" customWidth="1"/>
+    <col min="8" max="8" width="39.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="9.109375" customWidth="1"/>
+    <col min="18" max="18" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="D2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S2" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="str">
-        <f>VLOOKUP(G2,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(F2,"DDMM")</f>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="str">
+        <f>VLOOKUP(H3,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(G3,"DDMM")</f>
         <v>GY.MINI.0208</v>
       </c>
-      <c r="B2" s="1">
-        <f>F2-30</f>
+      <c r="B3" s="5" t="str">
+        <f>VLOOKUP(H3,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(G3,"DDMM")&amp;"."&amp;MSF[[#This Row],[Status-1]]</f>
+        <v>GY.MINI.0208.CNFD</v>
+      </c>
+      <c r="C3" s="1">
+        <f>G3-30</f>
         <v>46206</v>
       </c>
-      <c r="F2" s="1">
+      <c r="G3" s="1">
         <v>46236</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H3" t="s">
         <v>17</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3" t="s">
+        <v>79</v>
+      </c>
+      <c r="K3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" t="s">
+        <v>20</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="str">
+        <f>VLOOKUP(H4,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(G4,"DDMM")</f>
+        <v>NR.SWGL.0308</v>
+      </c>
+      <c r="B4" s="5" t="str">
+        <f>VLOOKUP(H4,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(G4,"DDMM")&amp;"."&amp;MSF[[#This Row],[Status-1]]</f>
+        <v>NR.SWGL.0308.CNFD</v>
+      </c>
+      <c r="C4" s="1">
+        <f t="shared" ref="C4:C15" si="0">G4-30</f>
+        <v>46207</v>
+      </c>
+      <c r="G4" s="1">
+        <v>46237</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
+        <v>79</v>
+      </c>
+      <c r="K4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4" t="s">
+        <v>20</v>
+      </c>
+      <c r="R4" t="s">
+        <v>22</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="str">
+        <f>VLOOKUP(H5,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(G5,"DDMM")</f>
+        <v>NR.EUCH.0408</v>
+      </c>
+      <c r="B5" s="5" t="str">
+        <f>VLOOKUP(H5,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(G5,"DDMM")&amp;"."&amp;MSF[[#This Row],[Status-1]]</f>
+        <v>NR.EUCH.0408.PNDG</v>
+      </c>
+      <c r="C5" s="1">
+        <f t="shared" si="0"/>
+        <v>46208</v>
+      </c>
+      <c r="G5" s="1">
+        <v>46238</v>
+      </c>
+      <c r="H5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
         <v>18</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K5" t="s">
         <v>19</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L5" t="s">
+        <v>29</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="str">
+        <f>VLOOKUP(H6,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(G6,"DDMM")</f>
+        <v>GY.MINI.0508</v>
+      </c>
+      <c r="B6" s="5" t="str">
+        <f>VLOOKUP(H6,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(G6,"DDMM")&amp;"."&amp;MSF[[#This Row],[Status-1]]</f>
+        <v>GY.MINI.0508.PNDG</v>
+      </c>
+      <c r="C6" s="1">
+        <f t="shared" si="0"/>
+        <v>46209</v>
+      </c>
+      <c r="G6" s="1">
+        <v>46239</v>
+      </c>
+      <c r="H6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="str">
+        <f>VLOOKUP(H7,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(G7,"DDMM")</f>
+        <v>NR.EUCH.0608</v>
+      </c>
+      <c r="B7" s="5" t="str">
+        <f>VLOOKUP(H7,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(G7,"DDMM")&amp;"."&amp;MSF[[#This Row],[Status-1]]</f>
+        <v>NR.EUCH.0608.PNDG</v>
+      </c>
+      <c r="C7" s="1">
+        <f t="shared" si="0"/>
+        <v>46210</v>
+      </c>
+      <c r="G7" s="1">
+        <v>46240</v>
+      </c>
+      <c r="H7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7" t="s">
+        <v>18</v>
+      </c>
+      <c r="K7" t="s">
+        <v>19</v>
+      </c>
+      <c r="L7" t="s">
+        <v>29</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="str">
+        <f>VLOOKUP(H8,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(G8,"DDMM")</f>
+        <v>GY.MGKE.0708</v>
+      </c>
+      <c r="B8" s="5" t="str">
+        <f>VLOOKUP(H8,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(G8,"DDMM")&amp;"."&amp;MSF[[#This Row],[Status-1]]</f>
+        <v>GY.MGKE.0708.PNDG</v>
+      </c>
+      <c r="C8" s="1">
+        <f t="shared" si="0"/>
+        <v>46211</v>
+      </c>
+      <c r="G8" s="1">
+        <v>46241</v>
+      </c>
+      <c r="H8" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" t="s">
+        <v>19</v>
+      </c>
+      <c r="L8" t="s">
+        <v>24</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="str">
+        <f>VLOOKUP(H9,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(G9,"DDMM")</f>
+        <v>NR.TAEU.0808</v>
+      </c>
+      <c r="B9" s="5" t="str">
+        <f>VLOOKUP(H9,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(G9,"DDMM")&amp;"."&amp;MSF[[#This Row],[Status-1]]</f>
+        <v>NR.TAEU.0808.PNDG</v>
+      </c>
+      <c r="C9" s="1">
+        <f t="shared" si="0"/>
+        <v>46212</v>
+      </c>
+      <c r="G9" s="1">
+        <v>46242</v>
+      </c>
+      <c r="H9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9" t="s">
+        <v>18</v>
+      </c>
+      <c r="K9" t="s">
+        <v>19</v>
+      </c>
+      <c r="L9" t="s">
+        <v>29</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="str">
+        <f>VLOOKUP(H10,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(G10,"DDMM")</f>
+        <v>NR.SWGL.0908</v>
+      </c>
+      <c r="B10" s="5" t="str">
+        <f>VLOOKUP(H10,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(G10,"DDMM")&amp;"."&amp;MSF[[#This Row],[Status-1]]</f>
+        <v>NR.SWGL.0908.PNDG</v>
+      </c>
+      <c r="C10" s="1">
+        <f t="shared" si="0"/>
+        <v>46213</v>
+      </c>
+      <c r="G10" s="1">
+        <v>46243</v>
+      </c>
+      <c r="H10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10" t="s">
+        <v>18</v>
+      </c>
+      <c r="K10" t="s">
+        <v>19</v>
+      </c>
+      <c r="L10" t="s">
+        <v>27</v>
+      </c>
+      <c r="R10" t="s">
+        <v>22</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="str">
+        <f>VLOOKUP(H11,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(G11,"DDMM")</f>
+        <v>DD.WHRL.1008</v>
+      </c>
+      <c r="B11" s="5" t="str">
+        <f>VLOOKUP(H11,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(G11,"DDMM")&amp;"."&amp;MSF[[#This Row],[Status-1]]</f>
+        <v>DD.WHRL.1008.PNDG</v>
+      </c>
+      <c r="C11" s="1">
+        <f t="shared" si="0"/>
+        <v>46214</v>
+      </c>
+      <c r="G11" s="1">
+        <v>46244</v>
+      </c>
+      <c r="H11" t="s">
+        <v>28</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11" t="s">
+        <v>18</v>
+      </c>
+      <c r="K11" t="s">
+        <v>19</v>
+      </c>
+      <c r="L11" t="s">
+        <v>29</v>
+      </c>
+      <c r="R11" t="s">
+        <v>22</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="str">
+        <f>VLOOKUP(H12,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(G12,"DDMM")</f>
+        <v>GY.MINI.1108</v>
+      </c>
+      <c r="B12" s="5" t="str">
+        <f>VLOOKUP(H12,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(G12,"DDMM")&amp;"."&amp;MSF[[#This Row],[Status-1]]</f>
+        <v>GY.MINI.1108.PNDG</v>
+      </c>
+      <c r="C12" s="1">
+        <f t="shared" si="0"/>
+        <v>46215</v>
+      </c>
+      <c r="G12" s="1">
+        <v>46245</v>
+      </c>
+      <c r="H12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12" t="s">
+        <v>18</v>
+      </c>
+      <c r="K12" t="s">
+        <v>19</v>
+      </c>
+      <c r="L12" t="s">
         <v>20</v>
       </c>
-      <c r="R2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="str">
-        <f>VLOOKUP(G3,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(F3,"DDMM")</f>
-        <v>NR.SWGL.0308</v>
-      </c>
-      <c r="B3" s="1">
-        <f t="shared" ref="B3:B14" si="0">F3-30</f>
-        <v>46207</v>
-      </c>
-      <c r="F3" s="1">
-        <v>46237</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="str">
+        <f>VLOOKUP(H13,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(G13,"DDMM")</f>
+        <v>NR.EUCH.1208</v>
+      </c>
+      <c r="B13" s="5" t="str">
+        <f>VLOOKUP(H13,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(G13,"DDMM")&amp;"."&amp;MSF[[#This Row],[Status-1]]</f>
+        <v>NR.EUCH.1208.PNDG</v>
+      </c>
+      <c r="C13" s="1">
+        <f t="shared" si="0"/>
+        <v>46216</v>
+      </c>
+      <c r="G13" s="1">
+        <v>46246</v>
+      </c>
+      <c r="H13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13" t="s">
         <v>18</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K13" t="s">
         <v>19</v>
       </c>
-      <c r="K3" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q3" t="s">
+      <c r="L13" t="s">
+        <v>29</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="str">
+        <f>VLOOKUP(H14,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(G14,"DDMM")</f>
+        <v>DD.FSME.1308</v>
+      </c>
+      <c r="B14" s="5" t="str">
+        <f>VLOOKUP(H14,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(G14,"DDMM")&amp;"."&amp;MSF[[#This Row],[Status-1]]</f>
+        <v>DD.FSME.1308.PNDG</v>
+      </c>
+      <c r="C14" s="1">
+        <f t="shared" si="0"/>
+        <v>46217</v>
+      </c>
+      <c r="G14" s="1">
+        <v>46247</v>
+      </c>
+      <c r="H14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14" t="s">
+        <v>18</v>
+      </c>
+      <c r="K14" t="s">
+        <v>19</v>
+      </c>
+      <c r="L14" t="s">
+        <v>29</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="str">
+        <f>VLOOKUP(H15,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(G15,"DDMM")</f>
+        <v>DD.MRVL.1408</v>
+      </c>
+      <c r="B15" s="5" t="str">
+        <f>VLOOKUP(H15,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(G15,"DDMM")&amp;"."&amp;MSF[[#This Row],[Status-1]]</f>
+        <v>DD.MRVL.1408.PNDG</v>
+      </c>
+      <c r="C15" s="1">
+        <f t="shared" si="0"/>
+        <v>46218</v>
+      </c>
+      <c r="G15" s="1">
+        <v>46248</v>
+      </c>
+      <c r="H15" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15" t="s">
+        <v>18</v>
+      </c>
+      <c r="K15" t="s">
+        <v>19</v>
+      </c>
+      <c r="L15" t="s">
+        <v>32</v>
+      </c>
+      <c r="R15" t="s">
         <v>22</v>
       </c>
-      <c r="R3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="str">
-        <f>VLOOKUP(G4,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(F4,"DDMM")</f>
-        <v>NR.EUCH.0408</v>
-      </c>
-      <c r="B4" s="1">
-        <f t="shared" si="0"/>
-        <v>46208</v>
-      </c>
-      <c r="F4" s="1">
-        <v>46238</v>
-      </c>
-      <c r="G4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" t="s">
-        <v>29</v>
-      </c>
-      <c r="R4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="str">
-        <f>VLOOKUP(G5,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(F5,"DDMM")</f>
-        <v>GY.MINI.0508</v>
-      </c>
-      <c r="B5" s="1">
-        <f t="shared" si="0"/>
-        <v>46209</v>
-      </c>
-      <c r="F5" s="1">
-        <v>46239</v>
-      </c>
-      <c r="G5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K5" t="s">
-        <v>24</v>
-      </c>
-      <c r="R5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="str">
-        <f>VLOOKUP(G6,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(F6,"DDMM")</f>
-        <v>NR.EUCH.0608</v>
-      </c>
-      <c r="B6" s="1">
-        <f t="shared" si="0"/>
-        <v>46210</v>
-      </c>
-      <c r="F6" s="1">
-        <v>46240</v>
-      </c>
-      <c r="G6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K6" t="s">
-        <v>29</v>
-      </c>
-      <c r="R6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="str">
-        <f>VLOOKUP(G7,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(F7,"DDMM")</f>
-        <v>GY.MGKE.0708</v>
-      </c>
-      <c r="B7" s="1">
-        <f t="shared" si="0"/>
-        <v>46211</v>
-      </c>
-      <c r="F7" s="1">
-        <v>46241</v>
-      </c>
-      <c r="G7" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K7" t="s">
-        <v>24</v>
-      </c>
-      <c r="R7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="str">
-        <f>VLOOKUP(G8,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(F8,"DDMM")</f>
-        <v>NR.TAEU.0808</v>
-      </c>
-      <c r="B8" s="1">
-        <f t="shared" si="0"/>
-        <v>46212</v>
-      </c>
-      <c r="F8" s="1">
-        <v>46242</v>
-      </c>
-      <c r="G8" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8" t="s">
-        <v>19</v>
-      </c>
-      <c r="K8" t="s">
-        <v>29</v>
-      </c>
-      <c r="R8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="str">
-        <f>VLOOKUP(G9,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(F9,"DDMM")</f>
-        <v>NR.SWGL.0908</v>
-      </c>
-      <c r="B9" s="1">
-        <f t="shared" si="0"/>
-        <v>46213</v>
-      </c>
-      <c r="F9" s="1">
-        <v>46243</v>
-      </c>
-      <c r="G9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9" t="s">
-        <v>19</v>
-      </c>
-      <c r="K9" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>22</v>
-      </c>
-      <c r="R9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="str">
-        <f>VLOOKUP(G10,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(F10,"DDMM")</f>
-        <v>DD.WHRL.1008</v>
-      </c>
-      <c r="B10" s="1">
-        <f t="shared" si="0"/>
-        <v>46214</v>
-      </c>
-      <c r="F10" s="1">
-        <v>46244</v>
-      </c>
-      <c r="G10" t="s">
-        <v>28</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10" t="s">
-        <v>19</v>
-      </c>
-      <c r="K10" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>22</v>
-      </c>
-      <c r="R10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="str">
-        <f>VLOOKUP(G11,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(F11,"DDMM")</f>
-        <v>GY.MINI.1108</v>
-      </c>
-      <c r="B11" s="1">
-        <f t="shared" si="0"/>
-        <v>46215</v>
-      </c>
-      <c r="F11" s="1">
-        <v>46245</v>
-      </c>
-      <c r="G11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11" t="s">
-        <v>19</v>
-      </c>
-      <c r="K11" t="s">
-        <v>20</v>
-      </c>
-      <c r="R11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="str">
-        <f>VLOOKUP(G12,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(F12,"DDMM")</f>
-        <v>NR.EUCH.1208</v>
-      </c>
-      <c r="B12" s="1">
-        <f t="shared" si="0"/>
-        <v>46216</v>
-      </c>
-      <c r="F12" s="1">
-        <v>46246</v>
-      </c>
-      <c r="G12" t="s">
-        <v>23</v>
-      </c>
-      <c r="H12">
-        <v>1</v>
-      </c>
-      <c r="I12" t="s">
-        <v>18</v>
-      </c>
-      <c r="J12" t="s">
-        <v>19</v>
-      </c>
-      <c r="K12" t="s">
-        <v>29</v>
-      </c>
-      <c r="R12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="str">
-        <f>VLOOKUP(G13,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(F13,"DDMM")</f>
-        <v>DD.FSME.1308</v>
-      </c>
-      <c r="B13" s="1">
-        <f t="shared" si="0"/>
-        <v>46217</v>
-      </c>
-      <c r="F13" s="1">
-        <v>46247</v>
-      </c>
-      <c r="G13" t="s">
-        <v>30</v>
-      </c>
-      <c r="H13">
-        <v>1</v>
-      </c>
-      <c r="I13" t="s">
-        <v>18</v>
-      </c>
-      <c r="J13" t="s">
-        <v>19</v>
-      </c>
-      <c r="K13" t="s">
-        <v>29</v>
-      </c>
-      <c r="R13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="str">
-        <f>VLOOKUP(G14,'RawData'!$A$2:$B$17,2,FALSE)&amp;"."&amp;TEXT(F14,"DDMM")</f>
-        <v>DD.MRVL.1408</v>
-      </c>
-      <c r="B14" s="1">
-        <f t="shared" si="0"/>
-        <v>46218</v>
-      </c>
-      <c r="F14" s="1">
-        <v>46248</v>
-      </c>
-      <c r="G14" t="s">
-        <v>31</v>
-      </c>
-      <c r="H14">
-        <v>1</v>
-      </c>
-      <c r="I14" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14" t="s">
-        <v>19</v>
-      </c>
-      <c r="K14" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>22</v>
-      </c>
-      <c r="R14" t="b">
+      <c r="S15" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1689,525 +2300,581 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T14"/>
+  <dimension ref="A2:U15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.21875" customWidth="1"/>
-    <col min="5" max="5" width="11.33203125" customWidth="1"/>
-    <col min="6" max="6" width="11.109375" customWidth="1"/>
-    <col min="7" max="7" width="39.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="9.77734375" customWidth="1"/>
-    <col min="11" max="11" width="9" customWidth="1"/>
-    <col min="12" max="12" width="9.44140625" customWidth="1"/>
-    <col min="17" max="17" width="11.21875" customWidth="1"/>
-    <col min="19" max="19" width="12.21875" customWidth="1"/>
+    <col min="2" max="2" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.21875" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
+    <col min="7" max="7" width="11.109375" customWidth="1"/>
+    <col min="8" max="8" width="39.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="9.77734375" customWidth="1"/>
+    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="13" max="13" width="9.44140625" customWidth="1"/>
+    <col min="18" max="18" width="11.21875" customWidth="1"/>
+    <col min="20" max="20" width="12.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B2" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="D2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T2" t="s">
         <v>33</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="str">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="str">
         <f>VLOOKUP(Louvre[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Louvre[[#This Row],[Tour Date]],"ddmm")</f>
         <v>GY.MINI.0208</v>
       </c>
-      <c r="B2" s="1">
-        <f t="shared" ref="B2:B14" si="0">F2-40</f>
+      <c r="B3" s="5" t="str">
+        <f>VLOOKUP(Louvre[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Louvre[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;Louvre[[#This Row],[Status-1]]</f>
+        <v>GY.MINI.0208.PNDG</v>
+      </c>
+      <c r="C3" s="1">
+        <f t="shared" ref="C3:C15" si="0">G3-40</f>
         <v>46196</v>
       </c>
-      <c r="F2" s="1">
+      <c r="G3" s="1">
         <v>46236</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H3" t="s">
         <v>17</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3" t="s">
         <v>18</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K3" t="s">
         <v>35</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L3" t="s">
         <v>36</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N3" t="s">
         <v>37</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O3" t="s">
         <v>38</v>
       </c>
-      <c r="T2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="str">
+      <c r="U3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="str">
         <f>VLOOKUP(Louvre[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Louvre[[#This Row],[Tour Date]],"ddmm")</f>
         <v>NR.SWGL.0308</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B4" s="5" t="str">
+        <f>VLOOKUP(Louvre[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Louvre[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;Louvre[[#This Row],[Status-1]]</f>
+        <v>NR.SWGL.0308.PNDG</v>
+      </c>
+      <c r="C4" s="1">
         <f t="shared" si="0"/>
         <v>46197</v>
       </c>
-      <c r="F3" s="1">
+      <c r="G4" s="1">
         <v>46237</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H4" t="s">
         <v>21</v>
       </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
         <v>18</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K4" t="s">
         <v>35</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L4" t="s">
         <v>36</v>
       </c>
-      <c r="T3" t="b">
+      <c r="U4" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="str">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="str">
         <f>VLOOKUP(Louvre[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Louvre[[#This Row],[Tour Date]],"ddmm")</f>
         <v>NR.EUCH.0408</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B5" s="5" t="str">
+        <f>VLOOKUP(Louvre[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Louvre[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;Louvre[[#This Row],[Status-1]]</f>
+        <v>NR.EUCH.0408.CNFD</v>
+      </c>
+      <c r="C5" s="1">
         <f t="shared" si="0"/>
         <v>46198</v>
       </c>
-      <c r="F4" s="1">
+      <c r="G5" s="1">
         <v>46238</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H5" t="s">
         <v>23</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" t="s">
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5" t="s">
+        <v>79</v>
+      </c>
+      <c r="K5" t="s">
         <v>35</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L5" t="s">
         <v>36</v>
       </c>
-      <c r="T4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="str">
+      <c r="U5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="str">
         <f>VLOOKUP(Louvre[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Louvre[[#This Row],[Tour Date]],"ddmm")</f>
         <v>GY.MINI.0508</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B6" s="5" t="str">
+        <f>VLOOKUP(Louvre[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Louvre[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;Louvre[[#This Row],[Status-1]]</f>
+        <v>GY.MINI.0508.CNFD</v>
+      </c>
+      <c r="C6" s="1">
         <f t="shared" si="0"/>
         <v>46199</v>
       </c>
-      <c r="F5" s="1">
+      <c r="G6" s="1">
         <v>46239</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H6" t="s">
         <v>17</v>
       </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
+        <v>79</v>
+      </c>
+      <c r="K6" t="s">
         <v>35</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L6" t="s">
         <v>36</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N6" t="s">
         <v>39</v>
       </c>
-      <c r="N5">
+      <c r="O6">
         <v>79043437</v>
       </c>
-      <c r="T5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="str">
+      <c r="U6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="str">
         <f>VLOOKUP(Louvre[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Louvre[[#This Row],[Tour Date]],"ddmm")</f>
         <v>NR.EUCH.0608</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B7" s="5" t="str">
+        <f>VLOOKUP(Louvre[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Louvre[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;Louvre[[#This Row],[Status-1]]</f>
+        <v>NR.EUCH.0608.PNDG</v>
+      </c>
+      <c r="C7" s="1">
         <f t="shared" si="0"/>
         <v>46200</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G7" s="1">
         <v>46240</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H7" t="s">
         <v>23</v>
       </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7" t="s">
         <v>18</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K7" t="s">
         <v>35</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L7" t="s">
         <v>36</v>
       </c>
-      <c r="T6" t="b">
+      <c r="U7" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="str">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="str">
         <f>VLOOKUP(Louvre[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Louvre[[#This Row],[Tour Date]],"ddmm")</f>
         <v>GY.MGKE.0708</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B8" s="5" t="str">
+        <f>VLOOKUP(Louvre[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Louvre[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;Louvre[[#This Row],[Status-1]]</f>
+        <v>GY.MGKE.0708.PNDG</v>
+      </c>
+      <c r="C8" s="1">
         <f t="shared" si="0"/>
         <v>46201</v>
       </c>
-      <c r="F7" s="1">
+      <c r="G8" s="1">
         <v>46241</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H8" t="s">
         <v>25</v>
       </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8" t="s">
         <v>18</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K8" t="s">
         <v>35</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L8" t="s">
         <v>36</v>
       </c>
-      <c r="M7" t="s">
+      <c r="N8" t="s">
         <v>40</v>
       </c>
-      <c r="N7">
+      <c r="O8">
         <v>79043461</v>
       </c>
-      <c r="T7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="str">
+      <c r="U8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="str">
         <f>VLOOKUP(Louvre[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Louvre[[#This Row],[Tour Date]],"ddmm")</f>
         <v>NR.TAEU.0808</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B9" s="5" t="str">
+        <f>VLOOKUP(Louvre[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Louvre[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;Louvre[[#This Row],[Status-1]]</f>
+        <v>NR.TAEU.0808.PNDG</v>
+      </c>
+      <c r="C9" s="1">
         <f t="shared" si="0"/>
         <v>46202</v>
       </c>
-      <c r="F8" s="1">
+      <c r="G9" s="1">
         <v>46242</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H9" t="s">
         <v>26</v>
       </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9" t="s">
         <v>18</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K9" t="s">
         <v>35</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L9" t="s">
         <v>36</v>
       </c>
-      <c r="M8" t="s">
+      <c r="N9" t="s">
         <v>41</v>
       </c>
-      <c r="N8">
+      <c r="O9">
         <v>79031584</v>
       </c>
-      <c r="S8" t="s">
+      <c r="T9" t="s">
         <v>22</v>
       </c>
-      <c r="T8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="str">
+      <c r="U9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="str">
         <f>VLOOKUP(Louvre[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Louvre[[#This Row],[Tour Date]],"ddmm")</f>
         <v>NR.SWGL.0908</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B10" s="5" t="str">
+        <f>VLOOKUP(Louvre[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Louvre[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;Louvre[[#This Row],[Status-1]]</f>
+        <v>NR.SWGL.0908.PNDG</v>
+      </c>
+      <c r="C10" s="1">
         <f t="shared" si="0"/>
         <v>46203</v>
       </c>
-      <c r="F9" s="1">
+      <c r="G10" s="1">
         <v>46243</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H10" t="s">
         <v>21</v>
       </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9" t="s">
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10" t="s">
         <v>18</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K10" t="s">
         <v>35</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L10" t="s">
         <v>36</v>
       </c>
-      <c r="T9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="str">
+      <c r="U10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="str">
         <f>VLOOKUP(Louvre[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Louvre[[#This Row],[Tour Date]],"ddmm")</f>
         <v>DD.WHRL.1008</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B11" s="5" t="str">
+        <f>VLOOKUP(Louvre[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Louvre[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;Louvre[[#This Row],[Status-1]]</f>
+        <v>DD.WHRL.1008.PNDG</v>
+      </c>
+      <c r="C11" s="1">
         <f t="shared" si="0"/>
         <v>46204</v>
       </c>
-      <c r="F10" s="1">
+      <c r="G11" s="1">
         <v>46244</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H11" t="s">
         <v>28</v>
       </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11" t="s">
         <v>18</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K11" t="s">
         <v>35</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L11" t="s">
         <v>36</v>
       </c>
-      <c r="T10" t="b">
+      <c r="U11" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="str">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="str">
         <f>VLOOKUP(Louvre[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Louvre[[#This Row],[Tour Date]],"ddmm")</f>
         <v>GY.MINI.1108</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B12" s="5" t="str">
+        <f>VLOOKUP(Louvre[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Louvre[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;Louvre[[#This Row],[Status-1]]</f>
+        <v>GY.MINI.1108.PNDG</v>
+      </c>
+      <c r="C12" s="1">
         <f t="shared" si="0"/>
         <v>46205</v>
       </c>
-      <c r="F11" s="1">
+      <c r="G12" s="1">
         <v>46245</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H12" t="s">
         <v>17</v>
       </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12" t="s">
         <v>18</v>
       </c>
-      <c r="J11" t="s">
+      <c r="K12" t="s">
         <v>35</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L12" t="s">
         <v>36</v>
       </c>
-      <c r="M11" t="s">
+      <c r="N12" t="s">
         <v>42</v>
       </c>
-      <c r="N11">
+      <c r="O12">
         <v>79030520</v>
       </c>
-      <c r="S11" t="s">
+      <c r="T12" t="s">
         <v>22</v>
       </c>
-      <c r="T11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="str">
+      <c r="U12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="str">
         <f>VLOOKUP(Louvre[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Louvre[[#This Row],[Tour Date]],"ddmm")</f>
         <v>NR.EUCH.1208</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B13" s="5" t="str">
+        <f>VLOOKUP(Louvre[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Louvre[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;Louvre[[#This Row],[Status-1]]</f>
+        <v>NR.EUCH.1208.PNDG</v>
+      </c>
+      <c r="C13" s="1">
         <f t="shared" si="0"/>
         <v>46206</v>
       </c>
-      <c r="F12" s="1">
+      <c r="G13" s="1">
         <v>46246</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H13" t="s">
         <v>23</v>
       </c>
-      <c r="H12">
-        <v>1</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13" t="s">
         <v>18</v>
       </c>
-      <c r="J12" t="s">
+      <c r="K13" t="s">
         <v>35</v>
       </c>
-      <c r="K12" t="s">
+      <c r="L13" t="s">
         <v>36</v>
       </c>
-      <c r="M12" t="s">
+      <c r="N13" t="s">
         <v>43</v>
       </c>
-      <c r="N12">
+      <c r="O13">
         <v>79043231</v>
       </c>
-      <c r="T12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="str">
+      <c r="U13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="str">
         <f>VLOOKUP(Louvre[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Louvre[[#This Row],[Tour Date]],"ddmm")</f>
         <v>DD.FSME.1308</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B14" s="5" t="str">
+        <f>VLOOKUP(Louvre[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Louvre[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;Louvre[[#This Row],[Status-1]]</f>
+        <v>DD.FSME.1308.PNDG</v>
+      </c>
+      <c r="C14" s="1">
         <f t="shared" si="0"/>
         <v>46207</v>
       </c>
-      <c r="F13" s="1">
+      <c r="G14" s="1">
         <v>46247</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H14" t="s">
         <v>30</v>
       </c>
-      <c r="H13">
-        <v>1</v>
-      </c>
-      <c r="I13" t="s">
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14" t="s">
         <v>18</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K14" t="s">
         <v>35</v>
       </c>
-      <c r="K13" t="s">
+      <c r="L14" t="s">
         <v>36</v>
       </c>
-      <c r="T13" t="b">
+      <c r="U14" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="str">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="str">
         <f>VLOOKUP(Louvre[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Louvre[[#This Row],[Tour Date]],"ddmm")</f>
         <v>DD.MRVL.1408</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B15" s="5" t="str">
+        <f>VLOOKUP(Louvre[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Louvre[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;Louvre[[#This Row],[Status-1]]</f>
+        <v>DD.MRVL.1408.PNDG</v>
+      </c>
+      <c r="C15" s="1">
         <f t="shared" si="0"/>
         <v>46208</v>
       </c>
-      <c r="F14" s="1">
+      <c r="G15" s="1">
         <v>46248</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H15" t="s">
         <v>31</v>
       </c>
-      <c r="H14">
-        <v>1</v>
-      </c>
-      <c r="I14" t="s">
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15" t="s">
         <v>18</v>
       </c>
-      <c r="J14" t="s">
+      <c r="K15" t="s">
         <v>35</v>
       </c>
-      <c r="K14" t="s">
+      <c r="L15" t="s">
         <v>36</v>
       </c>
-      <c r="T14" t="b">
+      <c r="U15" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2221,511 +2888,569 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:U15"/>
+  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.44140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="39.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.77734375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="80.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.21875" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.21875" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="32" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.5546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.77734375" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.44140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="66.88671875" style="7" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.5546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.88671875" style="7" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.33203125" style="7" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="8.88671875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B2" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="D2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J2" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T2" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U2" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="str">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A3" s="10" t="str">
         <f>VLOOKUP(Accor[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Accor[[#This Row],[Tour Date]],"ddmm")</f>
         <v>GY.MINI.0208</v>
       </c>
-      <c r="B2" s="2">
-        <f>F2-30</f>
+      <c r="B3" s="10" t="str">
+        <f>VLOOKUP(Accor[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Accor[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;Accor[[#This Row],[Status-1]]</f>
+        <v>GY.MINI.0208.PNDG</v>
+      </c>
+      <c r="C3" s="11">
+        <f>G3-30</f>
         <v>46206</v>
       </c>
-      <c r="E2" s="6"/>
-      <c r="F2" s="2">
+      <c r="F3" s="12"/>
+      <c r="G3" s="11">
         <v>46236</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="I3" s="7">
+        <v>1</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K3" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L3" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N3" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="T2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="str">
+      <c r="U3" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="str">
         <f>VLOOKUP(Accor[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Accor[[#This Row],[Tour Date]],"ddmm")</f>
         <v>NR.SWGL.0308</v>
       </c>
-      <c r="B3" s="2">
-        <f t="shared" ref="B3:B14" si="0">F3-30</f>
+      <c r="B4" s="10" t="str">
+        <f>VLOOKUP(Accor[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Accor[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;Accor[[#This Row],[Status-1]]</f>
+        <v>NR.SWGL.0308.PNDG</v>
+      </c>
+      <c r="C4" s="11">
+        <f t="shared" ref="C4:C15" si="0">G4-30</f>
         <v>46207</v>
       </c>
-      <c r="F3" s="2">
+      <c r="G4" s="11">
         <v>46237</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H4" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="I4" s="7">
+        <v>1</v>
+      </c>
+      <c r="J4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K4" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L4" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="T3" t="b">
+      <c r="U4" s="7" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="str">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="str">
         <f>VLOOKUP(Accor[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Accor[[#This Row],[Tour Date]],"ddmm")</f>
         <v>NR.EUCH.0408</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B5" s="10" t="str">
+        <f>VLOOKUP(Accor[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Accor[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;Accor[[#This Row],[Status-1]]</f>
+        <v>NR.EUCH.0408.PNDG</v>
+      </c>
+      <c r="C5" s="11">
         <f t="shared" si="0"/>
         <v>46208</v>
       </c>
-      <c r="F4" s="2">
+      <c r="G5" s="11">
         <v>46238</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H5" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="I5" s="7">
+        <v>1</v>
+      </c>
+      <c r="J5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K5" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L5" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N5" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="T4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="str">
+      <c r="U5" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="str">
         <f>VLOOKUP(Accor[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Accor[[#This Row],[Tour Date]],"ddmm")</f>
         <v>GY.MINI.0508</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B6" s="10" t="str">
+        <f>VLOOKUP(Accor[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Accor[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;Accor[[#This Row],[Status-1]]</f>
+        <v>GY.MINI.0508.PNDG</v>
+      </c>
+      <c r="C6" s="11">
         <f t="shared" si="0"/>
         <v>46209</v>
       </c>
-      <c r="F5" s="2">
+      <c r="G6" s="11">
         <v>46239</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H6" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="I6" s="7">
+        <v>1</v>
+      </c>
+      <c r="J6" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K6" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L6" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="T5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="str">
+      <c r="U6" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="str">
         <f>VLOOKUP(Accor[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Accor[[#This Row],[Tour Date]],"ddmm")</f>
         <v>NR.EUCH.0608</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B7" s="10" t="str">
+        <f>VLOOKUP(Accor[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Accor[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;Accor[[#This Row],[Status-1]]</f>
+        <v>NR.EUCH.0608.PNDG</v>
+      </c>
+      <c r="C7" s="11">
         <f t="shared" si="0"/>
         <v>46210</v>
       </c>
-      <c r="F6" s="2">
+      <c r="G7" s="11">
         <v>46240</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="I7" s="7">
+        <v>1</v>
+      </c>
+      <c r="J7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K7" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L7" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="M6" t="s">
+      <c r="N7" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="T6" t="b">
+      <c r="U7" s="7" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="str">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A8" s="10" t="str">
         <f>VLOOKUP(Accor[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Accor[[#This Row],[Tour Date]],"ddmm")</f>
         <v>GY.MGKE.0708</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B8" s="10" t="str">
+        <f>VLOOKUP(Accor[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Accor[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;Accor[[#This Row],[Status-1]]</f>
+        <v>GY.MGKE.0708.CNFD</v>
+      </c>
+      <c r="C8" s="11">
         <f t="shared" si="0"/>
         <v>46211</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G8" s="11">
         <v>46241</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H8" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="I8" s="7">
+        <v>1</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="K8" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L8" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="T7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="str">
+      <c r="U8" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="str">
         <f>VLOOKUP(Accor[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Accor[[#This Row],[Tour Date]],"ddmm")</f>
         <v>NR.TAEU.0808</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B9" s="10" t="str">
+        <f>VLOOKUP(Accor[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Accor[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;Accor[[#This Row],[Status-1]]</f>
+        <v>NR.TAEU.0808.CNFD</v>
+      </c>
+      <c r="C9" s="11">
         <f t="shared" si="0"/>
         <v>46212</v>
       </c>
-      <c r="F8" s="2">
+      <c r="G9" s="11">
         <v>46242</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H9" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8" t="s">
-        <v>18</v>
-      </c>
-      <c r="J8" t="s">
+      <c r="I9" s="7">
+        <v>1</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="K9" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="M8" t="s">
+      <c r="N9" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="T8" t="b">
+      <c r="U9" s="7" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="str">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="str">
         <f>VLOOKUP(Accor[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Accor[[#This Row],[Tour Date]],"ddmm")</f>
         <v>NR.SWGL.0908</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B10" s="10" t="str">
+        <f>VLOOKUP(Accor[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Accor[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;Accor[[#This Row],[Status-1]]</f>
+        <v>NR.SWGL.0908.PNDG</v>
+      </c>
+      <c r="C10" s="11">
         <f t="shared" si="0"/>
         <v>46213</v>
       </c>
-      <c r="F9" s="2">
+      <c r="G10" s="11">
         <v>46243</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H10" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9" t="s">
+      <c r="I10" s="7">
+        <v>1</v>
+      </c>
+      <c r="J10" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="J9" t="s">
+      <c r="K10" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L10" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="T9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="str">
+      <c r="U10" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="str">
         <f>VLOOKUP(Accor[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Accor[[#This Row],[Tour Date]],"ddmm")</f>
         <v>DD.WHRL.1008</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B11" s="10" t="str">
+        <f>VLOOKUP(Accor[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Accor[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;Accor[[#This Row],[Status-1]]</f>
+        <v>DD.WHRL.1008.PNDG</v>
+      </c>
+      <c r="C11" s="11">
         <f t="shared" si="0"/>
         <v>46214</v>
       </c>
-      <c r="F10" s="2">
+      <c r="G11" s="11">
         <v>46244</v>
       </c>
-      <c r="G10" t="s">
+      <c r="H11" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="I11" s="7">
+        <v>1</v>
+      </c>
+      <c r="J11" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K11" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L11" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="M10" t="s">
+      <c r="N11" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="T10" t="b">
+      <c r="U11" s="7" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="str">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="str">
         <f>VLOOKUP(Accor[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Accor[[#This Row],[Tour Date]],"ddmm")</f>
         <v>GY.MINI.1108</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B12" s="10" t="str">
+        <f>VLOOKUP(Accor[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Accor[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;Accor[[#This Row],[Status-1]]</f>
+        <v>GY.MINI.1108.PNDG</v>
+      </c>
+      <c r="C12" s="11">
         <f t="shared" si="0"/>
         <v>46215</v>
       </c>
-      <c r="F11" s="2">
+      <c r="G12" s="11">
         <v>46245</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H12" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="I12" s="7">
+        <v>1</v>
+      </c>
+      <c r="J12" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="J11" t="s">
+      <c r="K12" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L12" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="M11" t="s">
+      <c r="N12" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="T11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="str">
+      <c r="U12" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="str">
         <f>VLOOKUP(Accor[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Accor[[#This Row],[Tour Date]],"ddmm")</f>
         <v>NR.EUCH.1208</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B13" s="10" t="str">
+        <f>VLOOKUP(Accor[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Accor[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;Accor[[#This Row],[Status-1]]</f>
+        <v>NR.EUCH.1208.PNDG</v>
+      </c>
+      <c r="C13" s="11">
         <f t="shared" si="0"/>
         <v>46216</v>
       </c>
-      <c r="F12" s="2">
+      <c r="G13" s="11">
         <v>46246</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H13" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="H12">
-        <v>1</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="I13" s="7">
+        <v>1</v>
+      </c>
+      <c r="J13" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="J12" t="s">
+      <c r="K13" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="K12" t="s">
+      <c r="L13" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="T12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="str">
+      <c r="U13" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="str">
         <f>VLOOKUP(Accor[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Accor[[#This Row],[Tour Date]],"ddmm")</f>
         <v>DD.FSME.1308</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B14" s="10" t="str">
+        <f>VLOOKUP(Accor[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Accor[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;Accor[[#This Row],[Status-1]]</f>
+        <v>DD.FSME.1308.PNDG</v>
+      </c>
+      <c r="C14" s="11">
         <f t="shared" si="0"/>
         <v>46217</v>
       </c>
-      <c r="F13" s="2">
+      <c r="G14" s="11">
         <v>46247</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H14" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="H13">
-        <v>1</v>
-      </c>
-      <c r="I13" t="s">
+      <c r="I14" s="7">
+        <v>1</v>
+      </c>
+      <c r="J14" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K14" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="K13" t="s">
+      <c r="L14" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="T13" t="b">
+      <c r="U14" s="7" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="str">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="str">
         <f>VLOOKUP(Accor[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Accor[[#This Row],[Tour Date]],"ddmm")</f>
         <v>DD.MRVL.1408</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B15" s="10" t="str">
+        <f>VLOOKUP(Accor[[#This Row],[Tour Name]],RawData[#All],2,FALSE)&amp;"."&amp;TEXT(Accor[[#This Row],[Tour Date]],"ddmm")&amp;"."&amp;Accor[[#This Row],[Status-1]]</f>
+        <v>DD.MRVL.1408.PNDG</v>
+      </c>
+      <c r="C15" s="11">
         <f t="shared" si="0"/>
         <v>46218</v>
       </c>
-      <c r="F14" s="2">
+      <c r="G15" s="11">
         <v>46248</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H15" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H14">
-        <v>1</v>
-      </c>
-      <c r="I14" t="s">
+      <c r="I15" s="7">
+        <v>1</v>
+      </c>
+      <c r="J15" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="J14" t="s">
+      <c r="K15" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="K14" t="s">
+      <c r="L15" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="T14" t="b">
+      <c r="U15" s="7" t="b">
         <v>1</v>
       </c>
     </row>
